--- a/令和8年度収集カレンダー（縦通し）.xlsx
+++ b/令和8年度収集カレンダー（縦通し）.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annsyuu/Desktop/uenoseisou2.2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3093968E-9C86-DE43-AE33-0824499F7C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32FA2BD2-25E5-9A40-814A-44FCFB471CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4540" yWindow="600" windowWidth="28200" windowHeight="19880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="32740" windowHeight="19880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="A令和8年度収集カレンダー" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="80">
   <si>
     <t>2026年　４月</t>
   </si>
@@ -254,6 +254,14 @@
   </si>
   <si>
     <t>令和8年度　一般廃棄物収集カレンダー（４月〜３月）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>2027年　1１月</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>2027年　1２月</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -655,7 +663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G635"/>
+  <dimension ref="A1:O635"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="7" width="22" style="2" customWidth="1"/>
@@ -5917,7 +5925,7 @@
     </row>
     <row r="376" spans="1:7" ht="19">
       <c r="A376" s="3" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="B376" s="4"/>
       <c r="C376" s="4"/>
@@ -6700,7 +6708,7 @@
       <c r="F432" s="4"/>
       <c r="G432" s="4"/>
     </row>
-    <row r="433" spans="1:7">
+    <row r="433" spans="1:15">
       <c r="A433" s="4" t="s">
         <v>27</v>
       </c>
@@ -6711,7 +6719,7 @@
       <c r="F433" s="4"/>
       <c r="G433" s="4"/>
     </row>
-    <row r="434" spans="1:7">
+    <row r="434" spans="1:15">
       <c r="A434" s="4" t="s">
         <v>26</v>
       </c>
@@ -6722,7 +6730,7 @@
       <c r="F434" s="4"/>
       <c r="G434" s="4"/>
     </row>
-    <row r="435" spans="1:7">
+    <row r="435" spans="1:15">
       <c r="A435" s="4"/>
       <c r="B435" s="4"/>
       <c r="C435" s="4"/>
@@ -6731,7 +6739,7 @@
       <c r="F435" s="4"/>
       <c r="G435" s="4"/>
     </row>
-    <row r="436" spans="1:7">
+    <row r="436" spans="1:15">
       <c r="A436" s="4"/>
       <c r="B436" s="4"/>
       <c r="C436" s="4"/>
@@ -6740,7 +6748,7 @@
       <c r="F436" s="4"/>
       <c r="G436" s="4"/>
     </row>
-    <row r="437" spans="1:7">
+    <row r="437" spans="1:15">
       <c r="A437" s="4"/>
       <c r="B437" s="4"/>
       <c r="C437" s="4"/>
@@ -6749,9 +6757,9 @@
       <c r="F437" s="4"/>
       <c r="G437" s="4"/>
     </row>
-    <row r="438" spans="1:7" ht="19">
+    <row r="438" spans="1:15" ht="19">
       <c r="A438" s="3" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="B438" s="4"/>
       <c r="C438" s="4"/>
@@ -6759,8 +6767,15 @@
       <c r="E438" s="4"/>
       <c r="F438" s="4"/>
       <c r="G438" s="4"/>
-    </row>
-    <row r="439" spans="1:7" ht="17">
+      <c r="I438" s="3"/>
+      <c r="J438" s="4"/>
+      <c r="K438" s="4"/>
+      <c r="L438" s="4"/>
+      <c r="M438" s="4"/>
+      <c r="N438" s="4"/>
+      <c r="O438" s="4"/>
+    </row>
+    <row r="439" spans="1:15" ht="17">
       <c r="A439" s="5" t="s">
         <v>1</v>
       </c>
@@ -6782,59 +6797,137 @@
       <c r="G439" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="440" spans="1:7">
+      <c r="I439" s="5"/>
+      <c r="J439" s="5"/>
+      <c r="K439" s="5"/>
+      <c r="L439" s="5"/>
+      <c r="M439" s="5"/>
+      <c r="N439" s="5"/>
+      <c r="O439" s="5"/>
+    </row>
+    <row r="440" spans="1:15">
       <c r="A440" s="4"/>
-      <c r="B440" s="4"/>
-      <c r="C440" s="4"/>
-      <c r="D440" s="4"/>
-      <c r="E440" s="4" t="s">
-        <v>69</v>
+      <c r="B440" s="4">
+        <v>1</v>
+      </c>
+      <c r="C440" s="4">
+        <v>2</v>
+      </c>
+      <c r="D440" s="4">
+        <v>3</v>
+      </c>
+      <c r="E440" s="4">
+        <v>4</v>
       </c>
       <c r="F440" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G440" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="441" spans="1:7">
+        <v>6</v>
+      </c>
+      <c r="I440" s="4"/>
+      <c r="J440" s="4"/>
+      <c r="K440" s="4"/>
+      <c r="L440" s="4"/>
+      <c r="M440" s="4"/>
+      <c r="N440" s="4"/>
+      <c r="O440" s="4"/>
+    </row>
+    <row r="441" spans="1:15">
       <c r="A441" s="4"/>
-      <c r="B441" s="4"/>
-      <c r="C441" s="4"/>
-      <c r="D441" s="4"/>
-      <c r="E441" s="4"/>
+      <c r="B441" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C441" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D441" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E441" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="F441" s="4"/>
       <c r="G441" s="4"/>
-    </row>
-    <row r="442" spans="1:7">
+      <c r="I441" s="4"/>
+      <c r="J441" s="4"/>
+      <c r="K441" s="4"/>
+      <c r="L441" s="4"/>
+      <c r="M441" s="4"/>
+      <c r="N441" s="4"/>
+      <c r="O441" s="4"/>
+    </row>
+    <row r="442" spans="1:15">
       <c r="A442" s="4"/>
-      <c r="B442" s="4"/>
-      <c r="C442" s="4"/>
-      <c r="D442" s="4"/>
-      <c r="E442" s="4"/>
+      <c r="B442" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C442" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D442" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E442" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="F442" s="4"/>
       <c r="G442" s="4"/>
-    </row>
-    <row r="443" spans="1:7">
+      <c r="I442" s="4"/>
+      <c r="J442" s="4"/>
+      <c r="K442" s="4"/>
+      <c r="L442" s="4"/>
+      <c r="M442" s="4"/>
+      <c r="N442" s="4"/>
+      <c r="O442" s="4"/>
+    </row>
+    <row r="443" spans="1:15">
       <c r="A443" s="4"/>
-      <c r="B443" s="4"/>
-      <c r="C443" s="4"/>
-      <c r="D443" s="4"/>
-      <c r="E443" s="4"/>
+      <c r="B443" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C443" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D443" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E443" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="F443" s="4"/>
       <c r="G443" s="4"/>
-    </row>
-    <row r="444" spans="1:7">
+      <c r="I443" s="4"/>
+      <c r="J443" s="4"/>
+      <c r="K443" s="4"/>
+      <c r="L443" s="4"/>
+      <c r="M443" s="4"/>
+      <c r="N443" s="4"/>
+      <c r="O443" s="4"/>
+    </row>
+    <row r="444" spans="1:15">
       <c r="A444" s="4"/>
       <c r="B444" s="4"/>
-      <c r="C444" s="4"/>
-      <c r="D444" s="4"/>
-      <c r="E444" s="4"/>
+      <c r="C444" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D444" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E444" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="F444" s="4"/>
       <c r="G444" s="4"/>
-    </row>
-    <row r="445" spans="1:7">
+      <c r="I444" s="4"/>
+      <c r="J444" s="4"/>
+      <c r="K444" s="4"/>
+      <c r="L444" s="4"/>
+      <c r="M444" s="4"/>
+      <c r="N444" s="4"/>
+      <c r="O444" s="4"/>
+    </row>
+    <row r="445" spans="1:15">
       <c r="A445" s="4"/>
       <c r="B445" s="4"/>
       <c r="C445" s="4"/>
@@ -6842,8 +6935,15 @@
       <c r="E445" s="4"/>
       <c r="F445" s="4"/>
       <c r="G445" s="4"/>
-    </row>
-    <row r="446" spans="1:7">
+      <c r="I445" s="4"/>
+      <c r="J445" s="4"/>
+      <c r="K445" s="4"/>
+      <c r="L445" s="4"/>
+      <c r="M445" s="4"/>
+      <c r="N445" s="4"/>
+      <c r="O445" s="4"/>
+    </row>
+    <row r="446" spans="1:15">
       <c r="A446" s="4"/>
       <c r="B446" s="4"/>
       <c r="C446" s="4"/>
@@ -6851,8 +6951,15 @@
       <c r="E446" s="4"/>
       <c r="F446" s="4"/>
       <c r="G446" s="4"/>
-    </row>
-    <row r="447" spans="1:7">
+      <c r="I446" s="4"/>
+      <c r="J446" s="4"/>
+      <c r="K446" s="4"/>
+      <c r="L446" s="4"/>
+      <c r="M446" s="4"/>
+      <c r="N446" s="4"/>
+      <c r="O446" s="4"/>
+    </row>
+    <row r="447" spans="1:15">
       <c r="A447" s="4"/>
       <c r="B447" s="4"/>
       <c r="C447" s="4"/>
@@ -6860,8 +6967,15 @@
       <c r="E447" s="4"/>
       <c r="F447" s="4"/>
       <c r="G447" s="4"/>
-    </row>
-    <row r="448" spans="1:7">
+      <c r="I447" s="4"/>
+      <c r="J447" s="4"/>
+      <c r="K447" s="4"/>
+      <c r="L447" s="4"/>
+      <c r="M447" s="4"/>
+      <c r="N447" s="4"/>
+      <c r="O447" s="4"/>
+    </row>
+    <row r="448" spans="1:15">
       <c r="A448" s="4"/>
       <c r="B448" s="4"/>
       <c r="C448" s="4"/>
@@ -6869,8 +6983,15 @@
       <c r="E448" s="4"/>
       <c r="F448" s="4"/>
       <c r="G448" s="4"/>
-    </row>
-    <row r="449" spans="1:7">
+      <c r="I448" s="4"/>
+      <c r="J448" s="4"/>
+      <c r="K448" s="4"/>
+      <c r="L448" s="4"/>
+      <c r="M448" s="4"/>
+      <c r="N448" s="4"/>
+      <c r="O448" s="4"/>
+    </row>
+    <row r="449" spans="1:15">
       <c r="A449" s="4"/>
       <c r="B449" s="4"/>
       <c r="C449" s="4"/>
@@ -6878,31 +6999,45 @@
       <c r="E449" s="4"/>
       <c r="F449" s="4"/>
       <c r="G449" s="4"/>
-    </row>
-    <row r="450" spans="1:7">
+      <c r="I449" s="4"/>
+      <c r="J449" s="4"/>
+      <c r="K449" s="4"/>
+      <c r="L449" s="4"/>
+      <c r="M449" s="4"/>
+      <c r="N449" s="4"/>
+      <c r="O449" s="4"/>
+    </row>
+    <row r="450" spans="1:15">
       <c r="A450" s="4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B450" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C450" s="4">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D450" s="4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E450" s="4">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F450" s="4">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G450" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="451" spans="1:7">
+        <v>13</v>
+      </c>
+      <c r="I450" s="4"/>
+      <c r="J450" s="4"/>
+      <c r="K450" s="4"/>
+      <c r="L450" s="4"/>
+      <c r="M450" s="4"/>
+      <c r="N450" s="4"/>
+      <c r="O450" s="4"/>
+    </row>
+    <row r="451" spans="1:15">
       <c r="A451" s="4" t="s">
         <v>9</v>
       </c>
@@ -6910,7 +7045,7 @@
         <v>10</v>
       </c>
       <c r="C451" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D451" s="4" t="s">
         <v>9</v>
@@ -6920,8 +7055,15 @@
       </c>
       <c r="F451" s="4"/>
       <c r="G451" s="4"/>
-    </row>
-    <row r="452" spans="1:7">
+      <c r="I451" s="4"/>
+      <c r="J451" s="4"/>
+      <c r="K451" s="4"/>
+      <c r="L451" s="4"/>
+      <c r="M451" s="4"/>
+      <c r="N451" s="4"/>
+      <c r="O451" s="4"/>
+    </row>
+    <row r="452" spans="1:15">
       <c r="A452" s="4" t="s">
         <v>11</v>
       </c>
@@ -6929,7 +7071,7 @@
         <v>12</v>
       </c>
       <c r="C452" s="4" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="D452" s="4" t="s">
         <v>11</v>
@@ -6939,8 +7081,15 @@
       </c>
       <c r="F452" s="4"/>
       <c r="G452" s="4"/>
-    </row>
-    <row r="453" spans="1:7">
+      <c r="I452" s="4"/>
+      <c r="J452" s="4"/>
+      <c r="K452" s="4"/>
+      <c r="L452" s="4"/>
+      <c r="M452" s="4"/>
+      <c r="N452" s="4"/>
+      <c r="O452" s="4"/>
+    </row>
+    <row r="453" spans="1:15">
       <c r="A453" s="4" t="s">
         <v>13</v>
       </c>
@@ -6948,18 +7097,25 @@
         <v>17</v>
       </c>
       <c r="C453" s="4" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="D453" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E453" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F453" s="4"/>
       <c r="G453" s="4"/>
-    </row>
-    <row r="454" spans="1:7">
+      <c r="I453" s="4"/>
+      <c r="J453" s="4"/>
+      <c r="K453" s="4"/>
+      <c r="L453" s="4"/>
+      <c r="M453" s="4"/>
+      <c r="N453" s="4"/>
+      <c r="O453" s="4"/>
+    </row>
+    <row r="454" spans="1:15">
       <c r="A454" s="4" t="s">
         <v>23</v>
       </c>
@@ -6968,41 +7124,62 @@
       </c>
       <c r="C454" s="4"/>
       <c r="D454" s="4" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="E454" s="4" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F454" s="4"/>
       <c r="G454" s="4"/>
-    </row>
-    <row r="455" spans="1:7">
+      <c r="I454" s="4"/>
+      <c r="J454" s="4"/>
+      <c r="K454" s="4"/>
+      <c r="L454" s="4"/>
+      <c r="M454" s="4"/>
+      <c r="N454" s="4"/>
+      <c r="O454" s="4"/>
+    </row>
+    <row r="455" spans="1:15">
       <c r="A455" s="4" t="s">
         <v>27</v>
       </c>
       <c r="B455" s="4" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C455" s="4"/>
       <c r="D455" s="4" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E455" s="4"/>
       <c r="F455" s="4"/>
       <c r="G455" s="4"/>
-    </row>
-    <row r="456" spans="1:7">
+      <c r="I455" s="4"/>
+      <c r="J455" s="4"/>
+      <c r="K455" s="4"/>
+      <c r="L455" s="4"/>
+      <c r="M455" s="4"/>
+      <c r="N455" s="4"/>
+      <c r="O455" s="4"/>
+    </row>
+    <row r="456" spans="1:15">
       <c r="A456" s="4"/>
       <c r="B456" s="4"/>
       <c r="C456" s="4"/>
       <c r="D456" s="4" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E456" s="4"/>
       <c r="F456" s="4"/>
       <c r="G456" s="4"/>
-    </row>
-    <row r="457" spans="1:7">
+      <c r="I456" s="4"/>
+      <c r="J456" s="4"/>
+      <c r="K456" s="4"/>
+      <c r="L456" s="4"/>
+      <c r="M456" s="4"/>
+      <c r="N456" s="4"/>
+      <c r="O456" s="4"/>
+    </row>
+    <row r="457" spans="1:15">
       <c r="A457" s="4"/>
       <c r="B457" s="4"/>
       <c r="C457" s="4"/>
@@ -7010,8 +7187,15 @@
       <c r="E457" s="4"/>
       <c r="F457" s="4"/>
       <c r="G457" s="4"/>
-    </row>
-    <row r="458" spans="1:7">
+      <c r="I457" s="4"/>
+      <c r="J457" s="4"/>
+      <c r="K457" s="4"/>
+      <c r="L457" s="4"/>
+      <c r="M457" s="4"/>
+      <c r="N457" s="4"/>
+      <c r="O457" s="4"/>
+    </row>
+    <row r="458" spans="1:15">
       <c r="A458" s="4"/>
       <c r="B458" s="4"/>
       <c r="C458" s="4"/>
@@ -7019,8 +7203,15 @@
       <c r="E458" s="4"/>
       <c r="F458" s="4"/>
       <c r="G458" s="4"/>
-    </row>
-    <row r="459" spans="1:7">
+      <c r="I458" s="4"/>
+      <c r="J458" s="4"/>
+      <c r="K458" s="4"/>
+      <c r="L458" s="4"/>
+      <c r="M458" s="4"/>
+      <c r="N458" s="4"/>
+      <c r="O458" s="4"/>
+    </row>
+    <row r="459" spans="1:15">
       <c r="A459" s="4"/>
       <c r="B459" s="4"/>
       <c r="C459" s="4"/>
@@ -7028,31 +7219,45 @@
       <c r="E459" s="4"/>
       <c r="F459" s="4"/>
       <c r="G459" s="4"/>
-    </row>
-    <row r="460" spans="1:7">
-      <c r="A460" s="4" t="s">
-        <v>70</v>
+      <c r="I459" s="4"/>
+      <c r="J459" s="4"/>
+      <c r="K459" s="4"/>
+      <c r="L459" s="4"/>
+      <c r="M459" s="4"/>
+      <c r="N459" s="4"/>
+      <c r="O459" s="4"/>
+    </row>
+    <row r="460" spans="1:15">
+      <c r="A460" s="4">
+        <v>14</v>
       </c>
       <c r="B460" s="4">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C460" s="4">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D460" s="4">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E460" s="4">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F460" s="4">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G460" s="4">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="461" spans="1:7">
+        <v>20</v>
+      </c>
+      <c r="I460" s="4"/>
+      <c r="J460" s="4"/>
+      <c r="K460" s="4"/>
+      <c r="L460" s="4"/>
+      <c r="M460" s="4"/>
+      <c r="N460" s="4"/>
+      <c r="O460" s="4"/>
+    </row>
+    <row r="461" spans="1:15">
       <c r="A461" s="4" t="s">
         <v>9</v>
       </c>
@@ -7060,7 +7265,7 @@
         <v>10</v>
       </c>
       <c r="C461" s="4" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="D461" s="4" t="s">
         <v>9</v>
@@ -7070,8 +7275,15 @@
       </c>
       <c r="F461" s="4"/>
       <c r="G461" s="4"/>
-    </row>
-    <row r="462" spans="1:7">
+      <c r="I461" s="4"/>
+      <c r="J461" s="4"/>
+      <c r="K461" s="4"/>
+      <c r="L461" s="4"/>
+      <c r="M461" s="4"/>
+      <c r="N461" s="4"/>
+      <c r="O461" s="4"/>
+    </row>
+    <row r="462" spans="1:15">
       <c r="A462" s="4" t="s">
         <v>11</v>
       </c>
@@ -7079,7 +7291,7 @@
         <v>12</v>
       </c>
       <c r="C462" s="4" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="D462" s="4" t="s">
         <v>11</v>
@@ -7089,8 +7301,15 @@
       </c>
       <c r="F462" s="4"/>
       <c r="G462" s="4"/>
-    </row>
-    <row r="463" spans="1:7">
+      <c r="I462" s="4"/>
+      <c r="J462" s="4"/>
+      <c r="K462" s="4"/>
+      <c r="L462" s="4"/>
+      <c r="M462" s="4"/>
+      <c r="N462" s="4"/>
+      <c r="O462" s="4"/>
+    </row>
+    <row r="463" spans="1:15">
       <c r="A463" s="4" t="s">
         <v>13</v>
       </c>
@@ -7098,52 +7317,73 @@
         <v>17</v>
       </c>
       <c r="C463" s="4" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="D463" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E463" s="4" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F463" s="4"/>
       <c r="G463" s="4"/>
-    </row>
-    <row r="464" spans="1:7">
+      <c r="I463" s="4"/>
+      <c r="J463" s="4"/>
+      <c r="K463" s="4"/>
+      <c r="L463" s="4"/>
+      <c r="M463" s="4"/>
+      <c r="N463" s="4"/>
+      <c r="O463" s="4"/>
+    </row>
+    <row r="464" spans="1:15">
       <c r="A464" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B464" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C464" s="4"/>
+      <c r="C464" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="D464" s="4" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E464" s="4" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F464" s="4"/>
       <c r="G464" s="4"/>
-    </row>
-    <row r="465" spans="1:7">
+      <c r="I464" s="4"/>
+      <c r="J464" s="4"/>
+      <c r="K464" s="4"/>
+      <c r="L464" s="4"/>
+      <c r="M464" s="4"/>
+      <c r="N464" s="4"/>
+      <c r="O464" s="4"/>
+    </row>
+    <row r="465" spans="1:15">
       <c r="A465" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B465" s="4" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="C465" s="4"/>
       <c r="D465" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E465" s="4" t="s">
-        <v>20</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="E465" s="4"/>
       <c r="F465" s="4"/>
       <c r="G465" s="4"/>
-    </row>
-    <row r="466" spans="1:7">
+      <c r="I465" s="4"/>
+      <c r="J465" s="4"/>
+      <c r="K465" s="4"/>
+      <c r="L465" s="4"/>
+      <c r="M465" s="4"/>
+      <c r="N465" s="4"/>
+      <c r="O465" s="4"/>
+    </row>
+    <row r="466" spans="1:15">
       <c r="A466" s="4"/>
       <c r="B466" s="4"/>
       <c r="C466" s="4"/>
@@ -7151,8 +7391,15 @@
       <c r="E466" s="4"/>
       <c r="F466" s="4"/>
       <c r="G466" s="4"/>
-    </row>
-    <row r="467" spans="1:7">
+      <c r="I466" s="4"/>
+      <c r="J466" s="4"/>
+      <c r="K466" s="4"/>
+      <c r="L466" s="4"/>
+      <c r="M466" s="4"/>
+      <c r="N466" s="4"/>
+      <c r="O466" s="4"/>
+    </row>
+    <row r="467" spans="1:15">
       <c r="A467" s="4"/>
       <c r="B467" s="4"/>
       <c r="C467" s="4"/>
@@ -7160,8 +7407,15 @@
       <c r="E467" s="4"/>
       <c r="F467" s="4"/>
       <c r="G467" s="4"/>
-    </row>
-    <row r="468" spans="1:7">
+      <c r="I467" s="4"/>
+      <c r="J467" s="4"/>
+      <c r="K467" s="4"/>
+      <c r="L467" s="4"/>
+      <c r="M467" s="4"/>
+      <c r="N467" s="4"/>
+      <c r="O467" s="4"/>
+    </row>
+    <row r="468" spans="1:15">
       <c r="A468" s="4"/>
       <c r="B468" s="4"/>
       <c r="C468" s="4"/>
@@ -7169,8 +7423,15 @@
       <c r="E468" s="4"/>
       <c r="F468" s="4"/>
       <c r="G468" s="4"/>
-    </row>
-    <row r="469" spans="1:7">
+      <c r="I468" s="4"/>
+      <c r="J468" s="4"/>
+      <c r="K468" s="4"/>
+      <c r="L468" s="4"/>
+      <c r="M468" s="4"/>
+      <c r="N468" s="4"/>
+      <c r="O468" s="4"/>
+    </row>
+    <row r="469" spans="1:15">
       <c r="A469" s="4"/>
       <c r="B469" s="4"/>
       <c r="C469" s="4"/>
@@ -7178,31 +7439,45 @@
       <c r="E469" s="4"/>
       <c r="F469" s="4"/>
       <c r="G469" s="4"/>
-    </row>
-    <row r="470" spans="1:7">
+      <c r="I469" s="4"/>
+      <c r="J469" s="4"/>
+      <c r="K469" s="4"/>
+      <c r="L469" s="4"/>
+      <c r="M469" s="4"/>
+      <c r="N469" s="4"/>
+      <c r="O469" s="4"/>
+    </row>
+    <row r="470" spans="1:15">
       <c r="A470" s="4">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B470" s="4">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C470" s="4">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D470" s="4">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E470" s="4">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F470" s="4">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G470" s="4">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="471" spans="1:7">
+        <v>27</v>
+      </c>
+      <c r="I470" s="4"/>
+      <c r="J470" s="4"/>
+      <c r="K470" s="4"/>
+      <c r="L470" s="4"/>
+      <c r="M470" s="4"/>
+      <c r="N470" s="4"/>
+      <c r="O470" s="4"/>
+    </row>
+    <row r="471" spans="1:15">
       <c r="A471" s="4" t="s">
         <v>9</v>
       </c>
@@ -7210,7 +7485,7 @@
         <v>10</v>
       </c>
       <c r="C471" s="4" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D471" s="4" t="s">
         <v>9</v>
@@ -7220,8 +7495,15 @@
       </c>
       <c r="F471" s="4"/>
       <c r="G471" s="4"/>
-    </row>
-    <row r="472" spans="1:7">
+      <c r="I471" s="4"/>
+      <c r="J471" s="4"/>
+      <c r="K471" s="4"/>
+      <c r="L471" s="4"/>
+      <c r="M471" s="4"/>
+      <c r="N471" s="4"/>
+      <c r="O471" s="4"/>
+    </row>
+    <row r="472" spans="1:15">
       <c r="A472" s="4" t="s">
         <v>11</v>
       </c>
@@ -7229,7 +7511,7 @@
         <v>12</v>
       </c>
       <c r="C472" s="4" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="D472" s="4" t="s">
         <v>11</v>
@@ -7239,16 +7521,23 @@
       </c>
       <c r="F472" s="4"/>
       <c r="G472" s="4"/>
-    </row>
-    <row r="473" spans="1:7">
+      <c r="I472" s="4"/>
+      <c r="J472" s="4"/>
+      <c r="K472" s="4"/>
+      <c r="L472" s="4"/>
+      <c r="M472" s="4"/>
+      <c r="N472" s="4"/>
+      <c r="O472" s="4"/>
+    </row>
+    <row r="473" spans="1:15">
       <c r="A473" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B473" s="4" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="C473" s="4" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="D473" s="4" t="s">
         <v>13</v>
@@ -7258,55 +7547,75 @@
       </c>
       <c r="F473" s="4"/>
       <c r="G473" s="4"/>
-    </row>
-    <row r="474" spans="1:7">
+      <c r="I473" s="4"/>
+      <c r="J473" s="4"/>
+      <c r="K473" s="4"/>
+      <c r="L473" s="4"/>
+      <c r="M473" s="4"/>
+      <c r="N473" s="4"/>
+      <c r="O473" s="4"/>
+    </row>
+    <row r="474" spans="1:15">
       <c r="A474" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B474" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C474" s="4"/>
+      <c r="D474" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E474" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="C474" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D474" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E474" s="4" t="s">
-        <v>36</v>
       </c>
       <c r="F474" s="4"/>
       <c r="G474" s="4"/>
-    </row>
-    <row r="475" spans="1:7">
+      <c r="I474" s="4"/>
+      <c r="J474" s="4"/>
+      <c r="K474" s="4"/>
+      <c r="L474" s="4"/>
+      <c r="M474" s="4"/>
+      <c r="N474" s="4"/>
+      <c r="O474" s="4"/>
+    </row>
+    <row r="475" spans="1:15">
       <c r="A475" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B475" s="4" t="s">
-        <v>19</v>
-      </c>
+      <c r="B475" s="4"/>
       <c r="C475" s="4"/>
       <c r="D475" s="4" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="E475" s="4"/>
       <c r="F475" s="4"/>
       <c r="G475" s="4"/>
-    </row>
-    <row r="476" spans="1:7">
-      <c r="A476" s="4" t="s">
-        <v>26</v>
-      </c>
+      <c r="I475" s="4"/>
+      <c r="J475" s="4"/>
+      <c r="K475" s="4"/>
+      <c r="L475" s="4"/>
+      <c r="M475" s="4"/>
+      <c r="N475" s="4"/>
+      <c r="O475" s="4"/>
+    </row>
+    <row r="476" spans="1:15">
+      <c r="A476" s="4"/>
       <c r="B476" s="4"/>
       <c r="C476" s="4"/>
-      <c r="D476" s="4" t="s">
-        <v>35</v>
-      </c>
+      <c r="D476" s="4"/>
       <c r="E476" s="4"/>
       <c r="F476" s="4"/>
       <c r="G476" s="4"/>
-    </row>
-    <row r="477" spans="1:7">
+      <c r="I476" s="4"/>
+      <c r="J476" s="4"/>
+      <c r="K476" s="4"/>
+      <c r="L476" s="4"/>
+      <c r="M476" s="4"/>
+      <c r="N476" s="4"/>
+      <c r="O476" s="4"/>
+    </row>
+    <row r="477" spans="1:15">
       <c r="A477" s="4"/>
       <c r="B477" s="4"/>
       <c r="C477" s="4"/>
@@ -7314,8 +7623,15 @@
       <c r="E477" s="4"/>
       <c r="F477" s="4"/>
       <c r="G477" s="4"/>
-    </row>
-    <row r="478" spans="1:7">
+      <c r="I477" s="4"/>
+      <c r="J477" s="4"/>
+      <c r="K477" s="4"/>
+      <c r="L477" s="4"/>
+      <c r="M477" s="4"/>
+      <c r="N477" s="4"/>
+      <c r="O477" s="4"/>
+    </row>
+    <row r="478" spans="1:15">
       <c r="A478" s="4"/>
       <c r="B478" s="4"/>
       <c r="C478" s="4"/>
@@ -7323,8 +7639,15 @@
       <c r="E478" s="4"/>
       <c r="F478" s="4"/>
       <c r="G478" s="4"/>
-    </row>
-    <row r="479" spans="1:7">
+      <c r="I478" s="4"/>
+      <c r="J478" s="4"/>
+      <c r="K478" s="4"/>
+      <c r="L478" s="4"/>
+      <c r="M478" s="4"/>
+      <c r="N478" s="4"/>
+      <c r="O478" s="4"/>
+    </row>
+    <row r="479" spans="1:15">
       <c r="A479" s="4"/>
       <c r="B479" s="4"/>
       <c r="C479" s="4"/>
@@ -7332,122 +7655,129 @@
       <c r="E479" s="4"/>
       <c r="F479" s="4"/>
       <c r="G479" s="4"/>
-    </row>
-    <row r="480" spans="1:7">
+      <c r="I479" s="4"/>
+      <c r="J479" s="4"/>
+      <c r="K479" s="4"/>
+      <c r="L479" s="4"/>
+      <c r="M479" s="4"/>
+      <c r="N479" s="4"/>
+      <c r="O479" s="4"/>
+    </row>
+    <row r="480" spans="1:15">
       <c r="A480" s="4">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B480" s="4">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C480" s="4">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D480" s="4">
-        <v>28</v>
-      </c>
-      <c r="E480" s="4">
-        <v>29</v>
-      </c>
-      <c r="F480" s="4">
-        <v>30</v>
-      </c>
-      <c r="G480" s="4">
         <v>31</v>
       </c>
-    </row>
-    <row r="481" spans="1:7">
+      <c r="E480" s="4"/>
+      <c r="F480" s="4"/>
+      <c r="G480" s="4"/>
+      <c r="I480" s="4"/>
+      <c r="J480" s="4"/>
+      <c r="K480" s="4"/>
+      <c r="L480" s="4"/>
+      <c r="M480" s="4"/>
+      <c r="N480" s="4"/>
+      <c r="O480" s="4"/>
+    </row>
+    <row r="481" spans="1:15">
       <c r="A481" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B481" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C481" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D481" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E481" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="C481" s="4"/>
+      <c r="D481" s="4"/>
+      <c r="E481" s="4"/>
       <c r="F481" s="4"/>
       <c r="G481" s="4"/>
-    </row>
-    <row r="482" spans="1:7">
+      <c r="I481" s="4"/>
+      <c r="J481" s="4"/>
+      <c r="K481" s="4"/>
+      <c r="L481" s="4"/>
+      <c r="M481" s="4"/>
+      <c r="N481" s="4"/>
+      <c r="O481" s="4"/>
+    </row>
+    <row r="482" spans="1:15">
       <c r="A482" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B482" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C482" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D482" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E482" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="C482" s="4"/>
+      <c r="D482" s="4"/>
+      <c r="E482" s="4"/>
       <c r="F482" s="4"/>
       <c r="G482" s="4"/>
-    </row>
-    <row r="483" spans="1:7">
+      <c r="I482" s="4"/>
+      <c r="J482" s="4"/>
+      <c r="K482" s="4"/>
+      <c r="L482" s="4"/>
+      <c r="M482" s="4"/>
+      <c r="N482" s="4"/>
+      <c r="O482" s="4"/>
+    </row>
+    <row r="483" spans="1:15">
       <c r="A483" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B483" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C483" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D483" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E483" s="4" t="s">
-        <v>38</v>
-      </c>
+      <c r="B483" s="4"/>
+      <c r="C483" s="4"/>
+      <c r="D483" s="4"/>
+      <c r="E483" s="4"/>
       <c r="F483" s="4"/>
       <c r="G483" s="4"/>
-    </row>
-    <row r="484" spans="1:7">
-      <c r="A484" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B484" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C484" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D484" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E484" s="4" t="s">
-        <v>41</v>
-      </c>
+      <c r="I483" s="4"/>
+      <c r="J483" s="4"/>
+      <c r="K483" s="4"/>
+      <c r="L483" s="4"/>
+      <c r="M483" s="4"/>
+      <c r="N483" s="4"/>
+      <c r="O483" s="4"/>
+    </row>
+    <row r="484" spans="1:15">
+      <c r="A484" s="4"/>
+      <c r="B484" s="4"/>
+      <c r="C484" s="4"/>
+      <c r="D484" s="4"/>
+      <c r="E484" s="4"/>
       <c r="F484" s="4"/>
       <c r="G484" s="4"/>
-    </row>
-    <row r="485" spans="1:7">
-      <c r="A485" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B485" s="4" t="s">
-        <v>19</v>
-      </c>
+      <c r="I484" s="4"/>
+      <c r="J484" s="4"/>
+      <c r="K484" s="4"/>
+      <c r="L484" s="4"/>
+      <c r="M484" s="4"/>
+      <c r="N484" s="4"/>
+      <c r="O484" s="4"/>
+    </row>
+    <row r="485" spans="1:15">
+      <c r="A485" s="4"/>
+      <c r="B485" s="4"/>
       <c r="C485" s="4"/>
-      <c r="D485" s="4" t="s">
-        <v>43</v>
-      </c>
+      <c r="D485" s="4"/>
       <c r="E485" s="4"/>
       <c r="F485" s="4"/>
       <c r="G485" s="4"/>
-    </row>
-    <row r="486" spans="1:7">
+      <c r="I485" s="4"/>
+      <c r="J485" s="4"/>
+      <c r="K485" s="4"/>
+      <c r="L485" s="4"/>
+      <c r="M485" s="4"/>
+      <c r="N485" s="4"/>
+      <c r="O485" s="4"/>
+    </row>
+    <row r="486" spans="1:15">
       <c r="A486" s="4"/>
       <c r="B486" s="4"/>
       <c r="C486" s="4"/>
@@ -7455,8 +7785,15 @@
       <c r="E486" s="4"/>
       <c r="F486" s="4"/>
       <c r="G486" s="4"/>
-    </row>
-    <row r="487" spans="1:7">
+      <c r="I486" s="4"/>
+      <c r="J486" s="4"/>
+      <c r="K486" s="4"/>
+      <c r="L486" s="4"/>
+      <c r="M486" s="4"/>
+      <c r="N486" s="4"/>
+      <c r="O486" s="4"/>
+    </row>
+    <row r="487" spans="1:15">
       <c r="A487" s="4"/>
       <c r="B487" s="4"/>
       <c r="C487" s="4"/>
@@ -7464,8 +7801,15 @@
       <c r="E487" s="4"/>
       <c r="F487" s="4"/>
       <c r="G487" s="4"/>
-    </row>
-    <row r="488" spans="1:7">
+      <c r="I487" s="4"/>
+      <c r="J487" s="4"/>
+      <c r="K487" s="4"/>
+      <c r="L487" s="4"/>
+      <c r="M487" s="4"/>
+      <c r="N487" s="4"/>
+      <c r="O487" s="4"/>
+    </row>
+    <row r="488" spans="1:15">
       <c r="A488" s="4"/>
       <c r="B488" s="4"/>
       <c r="C488" s="4"/>
@@ -7473,8 +7817,15 @@
       <c r="E488" s="4"/>
       <c r="F488" s="4"/>
       <c r="G488" s="4"/>
-    </row>
-    <row r="489" spans="1:7">
+      <c r="I488" s="4"/>
+      <c r="J488" s="4"/>
+      <c r="K488" s="4"/>
+      <c r="L488" s="4"/>
+      <c r="M488" s="4"/>
+      <c r="N488" s="4"/>
+      <c r="O488" s="4"/>
+    </row>
+    <row r="489" spans="1:15">
       <c r="A489" s="4"/>
       <c r="B489" s="4"/>
       <c r="C489" s="4"/>
@@ -7482,10 +7833,17 @@
       <c r="E489" s="4"/>
       <c r="F489" s="4"/>
       <c r="G489" s="4"/>
-    </row>
-    <row r="490" spans="1:7" ht="19">
+      <c r="I489" s="4"/>
+      <c r="J489" s="4"/>
+      <c r="K489" s="4"/>
+      <c r="L489" s="4"/>
+      <c r="M489" s="4"/>
+      <c r="N489" s="4"/>
+      <c r="O489" s="4"/>
+    </row>
+    <row r="490" spans="1:15" ht="19">
       <c r="A490" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B490" s="4"/>
       <c r="C490" s="4"/>
@@ -7494,7 +7852,7 @@
       <c r="F490" s="4"/>
       <c r="G490" s="4"/>
     </row>
-    <row r="491" spans="1:7" ht="17">
+    <row r="491" spans="1:15" ht="17">
       <c r="A491" s="5" t="s">
         <v>1</v>
       </c>
@@ -7517,90 +7875,54 @@
         <v>7</v>
       </c>
     </row>
-    <row r="492" spans="1:7">
+    <row r="492" spans="1:15">
       <c r="A492" s="4"/>
-      <c r="B492" s="4">
-        <v>1</v>
-      </c>
-      <c r="C492" s="4">
+      <c r="B492" s="4"/>
+      <c r="C492" s="4"/>
+      <c r="D492" s="4"/>
+      <c r="E492" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F492" s="4">
         <v>2</v>
       </c>
-      <c r="D492" s="4">
+      <c r="G492" s="4">
         <v>3</v>
       </c>
-      <c r="E492" s="4">
-        <v>4</v>
-      </c>
-      <c r="F492" s="4">
-        <v>5</v>
-      </c>
-      <c r="G492" s="4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="493" spans="1:7">
+    </row>
+    <row r="493" spans="1:15">
       <c r="A493" s="4"/>
-      <c r="B493" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C493" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D493" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E493" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="B493" s="4"/>
+      <c r="C493" s="4"/>
+      <c r="D493" s="4"/>
+      <c r="E493" s="4"/>
       <c r="F493" s="4"/>
       <c r="G493" s="4"/>
     </row>
-    <row r="494" spans="1:7">
+    <row r="494" spans="1:15">
       <c r="A494" s="4"/>
-      <c r="B494" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C494" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D494" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E494" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="B494" s="4"/>
+      <c r="C494" s="4"/>
+      <c r="D494" s="4"/>
+      <c r="E494" s="4"/>
       <c r="F494" s="4"/>
       <c r="G494" s="4"/>
     </row>
-    <row r="495" spans="1:7">
+    <row r="495" spans="1:15">
       <c r="A495" s="4"/>
-      <c r="B495" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C495" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D495" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E495" s="4" t="s">
-        <v>17</v>
-      </c>
+      <c r="B495" s="4"/>
+      <c r="C495" s="4"/>
+      <c r="D495" s="4"/>
+      <c r="E495" s="4"/>
       <c r="F495" s="4"/>
       <c r="G495" s="4"/>
     </row>
-    <row r="496" spans="1:7">
+    <row r="496" spans="1:15">
       <c r="A496" s="4"/>
       <c r="B496" s="4"/>
-      <c r="C496" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D496" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E496" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="C496" s="4"/>
+      <c r="D496" s="4"/>
+      <c r="E496" s="4"/>
       <c r="F496" s="4"/>
       <c r="G496" s="4"/>
     </row>
@@ -7651,25 +7973,25 @@
     </row>
     <row r="502" spans="1:7">
       <c r="A502" s="4">
+        <v>4</v>
+      </c>
+      <c r="B502" s="4">
+        <v>5</v>
+      </c>
+      <c r="C502" s="4">
+        <v>6</v>
+      </c>
+      <c r="D502" s="4">
         <v>7</v>
       </c>
-      <c r="B502" s="4">
+      <c r="E502" s="4">
         <v>8</v>
       </c>
-      <c r="C502" s="4">
-        <v>9</v>
-      </c>
-      <c r="D502" s="4">
-        <v>10</v>
-      </c>
-      <c r="E502" s="4">
-        <v>11</v>
-      </c>
       <c r="F502" s="4">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G502" s="4">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="503" spans="1:7">
@@ -7680,7 +8002,7 @@
         <v>10</v>
       </c>
       <c r="C503" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D503" s="4" t="s">
         <v>9</v>
@@ -7699,7 +8021,7 @@
         <v>12</v>
       </c>
       <c r="C504" s="4" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D504" s="4" t="s">
         <v>11</v>
@@ -7718,13 +8040,13 @@
         <v>17</v>
       </c>
       <c r="C505" s="4" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D505" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E505" s="4" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F505" s="4"/>
       <c r="G505" s="4"/>
@@ -7738,10 +8060,10 @@
       </c>
       <c r="C506" s="4"/>
       <c r="D506" s="4" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="E506" s="4" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F506" s="4"/>
       <c r="G506" s="4"/>
@@ -7751,11 +8073,11 @@
         <v>27</v>
       </c>
       <c r="B507" s="4" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C507" s="4"/>
       <c r="D507" s="4" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="E507" s="4"/>
       <c r="F507" s="4"/>
@@ -7766,7 +8088,7 @@
       <c r="B508" s="4"/>
       <c r="C508" s="4"/>
       <c r="D508" s="4" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="E508" s="4"/>
       <c r="F508" s="4"/>
@@ -7800,26 +8122,26 @@
       <c r="G511" s="4"/>
     </row>
     <row r="512" spans="1:7">
-      <c r="A512" s="4">
+      <c r="A512" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B512" s="4">
+        <v>12</v>
+      </c>
+      <c r="C512" s="4">
+        <v>13</v>
+      </c>
+      <c r="D512" s="4">
         <v>14</v>
       </c>
-      <c r="B512" s="4">
+      <c r="E512" s="4">
         <v>15</v>
       </c>
-      <c r="C512" s="4">
+      <c r="F512" s="4">
         <v>16</v>
       </c>
-      <c r="D512" s="4">
+      <c r="G512" s="4">
         <v>17</v>
-      </c>
-      <c r="E512" s="4">
-        <v>18</v>
-      </c>
-      <c r="F512" s="4">
-        <v>19</v>
-      </c>
-      <c r="G512" s="4">
-        <v>20</v>
       </c>
     </row>
     <row r="513" spans="1:7">
@@ -7830,7 +8152,7 @@
         <v>10</v>
       </c>
       <c r="C513" s="4" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="D513" s="4" t="s">
         <v>9</v>
@@ -7849,7 +8171,7 @@
         <v>12</v>
       </c>
       <c r="C514" s="4" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="D514" s="4" t="s">
         <v>11</v>
@@ -7868,48 +8190,48 @@
         <v>17</v>
       </c>
       <c r="C515" s="4" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="D515" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E515" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F515" s="4"/>
       <c r="G515" s="4"/>
     </row>
     <row r="516" spans="1:7">
       <c r="A516" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B516" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C516" s="4" t="s">
-        <v>27</v>
-      </c>
+      <c r="C516" s="4"/>
       <c r="D516" s="4" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="E516" s="4" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F516" s="4"/>
       <c r="G516" s="4"/>
     </row>
     <row r="517" spans="1:7">
       <c r="A517" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B517" s="4" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="C517" s="4"/>
       <c r="D517" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E517" s="4"/>
+        <v>26</v>
+      </c>
+      <c r="E517" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="F517" s="4"/>
       <c r="G517" s="4"/>
     </row>
@@ -7951,25 +8273,25 @@
     </row>
     <row r="522" spans="1:7">
       <c r="A522" s="4">
+        <v>18</v>
+      </c>
+      <c r="B522" s="4">
+        <v>19</v>
+      </c>
+      <c r="C522" s="4">
+        <v>20</v>
+      </c>
+      <c r="D522" s="4">
         <v>21</v>
       </c>
-      <c r="B522" s="4">
+      <c r="E522" s="4">
         <v>22</v>
       </c>
-      <c r="C522" s="4">
+      <c r="F522" s="4">
         <v>23</v>
       </c>
-      <c r="D522" s="4">
+      <c r="G522" s="4">
         <v>24</v>
-      </c>
-      <c r="E522" s="4">
-        <v>25</v>
-      </c>
-      <c r="F522" s="4">
-        <v>26</v>
-      </c>
-      <c r="G522" s="4">
-        <v>27</v>
       </c>
     </row>
     <row r="523" spans="1:7">
@@ -7980,7 +8302,7 @@
         <v>10</v>
       </c>
       <c r="C523" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D523" s="4" t="s">
         <v>9</v>
@@ -7999,7 +8321,7 @@
         <v>12</v>
       </c>
       <c r="C524" s="4" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="D524" s="4" t="s">
         <v>11</v>
@@ -8015,10 +8337,10 @@
         <v>13</v>
       </c>
       <c r="B525" s="4" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C525" s="4" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="D525" s="4" t="s">
         <v>13</v>
@@ -8034,14 +8356,16 @@
         <v>23</v>
       </c>
       <c r="B526" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C526" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="C526" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="D526" s="4" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="E526" s="4" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F526" s="4"/>
       <c r="G526" s="4"/>
@@ -8050,20 +8374,26 @@
       <c r="A527" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B527" s="4"/>
+      <c r="B527" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="C527" s="4"/>
       <c r="D527" s="4" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E527" s="4"/>
       <c r="F527" s="4"/>
       <c r="G527" s="4"/>
     </row>
     <row r="528" spans="1:7">
-      <c r="A528" s="4"/>
+      <c r="A528" s="4" t="s">
+        <v>26</v>
+      </c>
       <c r="B528" s="4"/>
       <c r="C528" s="4"/>
-      <c r="D528" s="4"/>
+      <c r="D528" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="E528" s="4"/>
       <c r="F528" s="4"/>
       <c r="G528" s="4"/>
@@ -8097,20 +8427,26 @@
     </row>
     <row r="532" spans="1:7">
       <c r="A532" s="4">
+        <v>25</v>
+      </c>
+      <c r="B532" s="4">
+        <v>26</v>
+      </c>
+      <c r="C532" s="4">
+        <v>27</v>
+      </c>
+      <c r="D532" s="4">
         <v>28</v>
       </c>
-      <c r="B532" s="4">
+      <c r="E532" s="4">
         <v>29</v>
       </c>
-      <c r="C532" s="4">
+      <c r="F532" s="4">
         <v>30</v>
       </c>
-      <c r="D532" s="4">
+      <c r="G532" s="4">
         <v>31</v>
       </c>
-      <c r="E532" s="4"/>
-      <c r="F532" s="4"/>
-      <c r="G532" s="4"/>
     </row>
     <row r="533" spans="1:7">
       <c r="A533" s="4" t="s">
@@ -8119,9 +8455,15 @@
       <c r="B533" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C533" s="4"/>
-      <c r="D533" s="4"/>
-      <c r="E533" s="4"/>
+      <c r="C533" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D533" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E533" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="F533" s="4"/>
       <c r="G533" s="4"/>
     </row>
@@ -8132,9 +8474,15 @@
       <c r="B534" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C534" s="4"/>
-      <c r="D534" s="4"/>
-      <c r="E534" s="4"/>
+      <c r="C534" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D534" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E534" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="F534" s="4"/>
       <c r="G534" s="4"/>
     </row>
@@ -8142,27 +8490,51 @@
       <c r="A535" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B535" s="4"/>
-      <c r="C535" s="4"/>
-      <c r="D535" s="4"/>
-      <c r="E535" s="4"/>
+      <c r="B535" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C535" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D535" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E535" s="4" t="s">
+        <v>38</v>
+      </c>
       <c r="F535" s="4"/>
       <c r="G535" s="4"/>
     </row>
     <row r="536" spans="1:7">
-      <c r="A536" s="4"/>
-      <c r="B536" s="4"/>
-      <c r="C536" s="4"/>
-      <c r="D536" s="4"/>
-      <c r="E536" s="4"/>
+      <c r="A536" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B536" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C536" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D536" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E536" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="F536" s="4"/>
       <c r="G536" s="4"/>
     </row>
     <row r="537" spans="1:7">
-      <c r="A537" s="4"/>
-      <c r="B537" s="4"/>
+      <c r="A537" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B537" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="C537" s="4"/>
-      <c r="D537" s="4"/>
+      <c r="D537" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="E537" s="4"/>
       <c r="F537" s="4"/>
       <c r="G537" s="4"/>

--- a/令和8年度収集カレンダー（縦通し）.xlsx
+++ b/令和8年度収集カレンダー（縦通し）.xlsx
@@ -7214,7 +7214,7 @@
     <row r="376" ht="19" customHeight="1">
       <c r="A376" s="3" t="inlineStr">
         <is>
-          <t>2027年　1１月</t>
+          <t>2026年　１１月</t>
         </is>
       </c>
       <c r="B376" s="4" t="n"/>
@@ -8268,7 +8268,7 @@
     <row r="438" ht="19" customHeight="1">
       <c r="A438" s="3" t="inlineStr">
         <is>
-          <t>2027年　1２月</t>
+          <t>2026年　１２月</t>
         </is>
       </c>
       <c r="B438" s="4" t="n"/>
